--- a/tabular/unified-taxonomy.xlsx
+++ b/tabular/unified-taxonomy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/erv/ERVdb-HomoSapiens/tabular/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2528A5DA-D600-5C43-98F1-D1C16859CCD3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA94A31F-AD22-BD42-8D9B-55BBB0358CE0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="880" yWindow="500" windowWidth="26240" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
